--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>SMFG</t>
   </si>
@@ -656,123 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27541900</v>
+      </c>
+      <c r="E8" s="3">
         <v>21868000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23465200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26836000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23147300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25911200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20865300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26062900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30828400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12887100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13732100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16138200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16534000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15686800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15461400</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,39 +824,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>27541900</v>
+      </c>
+      <c r="E10" s="3">
         <v>21868000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23465200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26836000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23147300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25911200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20865300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>26062900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30828400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,39 +998,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E14" s="3">
         <v>154100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>92400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2206300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>836800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>482800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>804900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>894200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>609600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,39 +1049,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>424800</v>
+      </c>
+      <c r="E15" s="3">
         <v>523700</v>
       </c>
-      <c r="E15" s="3">
-        <v>621100</v>
-      </c>
       <c r="F15" s="3">
+        <v>2238100</v>
+      </c>
+      <c r="G15" s="3">
         <v>2424800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2645100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2803800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2946700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1975600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2920600</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1072,15 +1094,18 @@
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-1185200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1099400</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18507000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18297700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16447900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15794900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16650600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17109100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17656100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18023700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20147100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4738300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3929800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3297800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2380800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2923100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2835200</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9034900</v>
+      </c>
+      <c r="E18" s="3">
         <v>3570300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7017300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11041100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6496700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8802100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3209300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8039200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10681200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8148800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9802300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12840400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14153200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12763800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12626200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,104 +1244,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-832000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-952800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1060300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-657700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>89300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-328900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-223300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-362400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-464400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1548300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2598000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1671400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1121300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4503500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4386900</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10291700</v>
+      </c>
+      <c r="E21" s="3">
         <v>5046800</v>
       </c>
-      <c r="E21" s="3">
-        <v>8698700</v>
-      </c>
       <c r="F21" s="3">
+        <v>10315600</v>
+      </c>
+      <c r="G21" s="3">
         <v>14123600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9052500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11934800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6379300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10377200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14066200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8660400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9140900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13315400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15152100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10302300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9804500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9779800</v>
+      </c>
+      <c r="E23" s="3">
         <v>4369000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7985100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9492500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5570600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8648200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2627700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7507400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10536000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6600500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7204200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11169000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13031900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8260200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8239300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2264500</v>
+      </c>
+      <c r="E24" s="3">
         <v>920200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2063000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2452500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1329000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2273100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>481100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1663300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2159800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1152200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1654100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3764800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4202700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2319400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4162400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7515200</v>
+      </c>
+      <c r="E26" s="3">
         <v>3448800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5922100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7040000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4241600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6375100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2146600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5844100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8376200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5448300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5550200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7404200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8829200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5940900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4076900</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7154200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3192900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5774000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6859300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4113900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6216000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1859200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4890600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7155900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4761900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4753100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6428300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7651900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3743300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3058400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>832000</v>
+      </c>
+      <c r="E32" s="3">
         <v>952800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1060300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>657700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-89300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>328900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>223300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>362400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>464400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1548300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2598000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1671400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1121300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4503500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4386900</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7467800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3404200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5865000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6944400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4202300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6334600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1974100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4997800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7247500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4761900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4753100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6428300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7651900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3743300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3058400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7467800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3404200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5865000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6944400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4202300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6334600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1974100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4997800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7247500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4761900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4753100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6428300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7651900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3743300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3058400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,134 +2158,141 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>442528000</v>
+      </c>
+      <c r="E41" s="3">
         <v>487471200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>498713000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>550748900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>594505200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>629818900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>552104400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>495290400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>486604000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>315874000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>314501000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>339059000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>302199000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>217778000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84465200</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>252078600</v>
+      </c>
+      <c r="E42" s="3">
         <v>233004900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>191656400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>171137600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>168849300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>180629900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>204998100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>139258100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>135756600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>164672000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>174560000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>189608000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>163523000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>183032000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>39736300</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>43202500</v>
+      </c>
+      <c r="E43" s="3">
         <v>22262600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16873500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7577300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12766600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12007200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12854200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11758300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11896400</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2216,9 +2308,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2246,8 +2341,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2264,39 +2359,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36627100</v>
+      </c>
+      <c r="E45" s="3">
         <v>27049200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24958700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24726300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22819600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21344300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22673300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23372400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>80885200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2312,39 +2410,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>804676700</v>
+      </c>
+      <c r="E46" s="3">
         <v>798281200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>765808600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>793910300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>838972800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>879653400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>829638300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>700809500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>746511900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,153 +2461,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>239921600</v>
+      </c>
+      <c r="E47" s="3">
         <v>253970300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>225245500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>227335200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>291923100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>304513200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>221768500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>181503800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>196685300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4074700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4486600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4979100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3411000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4711900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1868200</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8619700</v>
+      </c>
+      <c r="E48" s="3">
         <v>8808100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8906100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13783100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14518100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15865100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16399400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13606900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14219000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20905100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21457800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23635400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21496600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36213000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20247600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7814000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7286900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6780300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6808100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8176000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7411600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7764500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7416200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7870600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6379500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6455200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6990800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7510200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15399600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16256900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12568400</v>
+      </c>
+      <c r="E52" s="3">
         <v>11536200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12470900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11658100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11659500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10719800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6994600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20026600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24734100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2547200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2418900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4299900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2684900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7796700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8355100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1944615800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1951044900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1859585700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1938458500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2043586200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2125019100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1971696300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1764313900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1809477600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1333120000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1371410000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1564770000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1479660000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1343090000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1281880000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,8 +2914,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2814,8 +2944,8 @@
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2832,41 +2962,44 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>312272600</v>
+      </c>
+      <c r="E58" s="3">
         <v>341151300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>306827000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>290158800</v>
       </c>
-      <c r="G58" s="3">
-        <v>344188400</v>
-      </c>
       <c r="H58" s="3">
+        <v>346234900</v>
+      </c>
+      <c r="I58" s="3">
         <v>338466400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>362316300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>194585100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>198449300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2880,57 +3013,63 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40574700</v>
+      </c>
+      <c r="E59" s="3">
         <v>43521100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42475500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33107100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>33915800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26022500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25117300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25715900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>60796000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>542000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>521300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>654300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>681000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4547000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2359800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2958,8 +3097,8 @@
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="L60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -2976,105 +3115,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>116900000</v>
+      </c>
+      <c r="E61" s="3">
         <v>129177800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>139050600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>166494600</v>
       </c>
-      <c r="G61" s="3">
-        <v>174409800</v>
-      </c>
       <c r="H61" s="3">
+        <v>172363300</v>
+      </c>
+      <c r="I61" s="3">
         <v>185333400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>146441500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>188070300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>176558400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>127494000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>115272000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>137357000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>110944000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>58862700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>94132200</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31161500</v>
+      </c>
+      <c r="E62" s="3">
         <v>29238900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28095000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28219100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28057900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27814000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28515100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22128600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21792300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4210400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5131000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7540600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3803400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6030000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1152100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1829594300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1840935900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1751958900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1836626200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1938329900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2014022200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1870072900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1658064900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1691820200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1267500000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1305870000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1487790000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1412960000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1284350000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1233310000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53993200</v>
+      </c>
+      <c r="E72" s="3">
         <v>52331600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>51365100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>54158300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>52988500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>54957200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52135200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51575700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>48483500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33971200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33349600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>34979000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31894000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57285400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21765900</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>113894200</v>
+      </c>
+      <c r="E76" s="3">
         <v>109107100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>106720700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>101033500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>104487800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>110378700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101063000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>101789800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>106047900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>65614000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>65537400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>76979300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>66693800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58740700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48567700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7467800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3404200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5865000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6944400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4202300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6334600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1974100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4997800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7247500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4761900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4753100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6428300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7651900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3743300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3058400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>875200</v>
+      </c>
+      <c r="E83" s="3">
         <v>927400</v>
       </c>
-      <c r="E83" s="3">
-        <v>1027300</v>
-      </c>
       <c r="F83" s="3">
+        <v>2238100</v>
+      </c>
+      <c r="G83" s="3">
         <v>2424800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2645100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2803800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2946700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1975600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2920600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2050700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1955200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2121500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2111000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2037600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1563500</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-109021300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-33294900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-45517200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-111444300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8206300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14596900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41896000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21150400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49818300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30446700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8285300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>69840100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>76062400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21574500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11941900</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1078700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-657800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-791400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-661900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-670100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1009400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-780200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4592000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6693100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3341800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3890100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4938600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4260700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5273500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1175100</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17358300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30256100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5398500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>43625100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21932800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-70352000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27812900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10843500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33837200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3918300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>38521000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12429800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>133008000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12797800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22347400</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3710200</v>
+      </c>
+      <c r="E96" s="3">
         <v>2963400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2391800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2353900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2345200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2533800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2491900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2323500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2149500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1382200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1557800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1457900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1557000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2458000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1283000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>67185400</v>
+      </c>
+      <c r="E100" s="3">
         <v>49681300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>53469500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>68570000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>45290900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>144879600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30143600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>39690700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>51977100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1122400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-411600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2581100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9515500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6725300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2759000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8044800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-739400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>11287600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6773800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7866900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4413000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2526700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>397600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-431900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-71100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-731900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1515800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>51100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5676200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-557600</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16432800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14609100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13841300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7524700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>23018700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>93537500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>41700100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29781400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>67526400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33171500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29092200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>56345100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>199606000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>33323200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13722100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
